--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17FDE4E-E26A-4BFE-9AEC-F8EC084BC6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA244B3D-6C3D-4F3E-9367-087BFD6AF679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
   <si>
     <t>Auteur:</t>
   </si>
@@ -218,6 +218,18 @@
   </si>
   <si>
     <t>Analyse conceptuelle des routes Api à faire</t>
+  </si>
+  <si>
+    <t>Fix ma db et docker qui avait des prbl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place API Rest </t>
+  </si>
+  <si>
+    <t>Analyse route API a faire et relecture du cdc</t>
+  </si>
+  <si>
+    <t>Création des routes simple (get livre) et create livre pas encore fini (il faut s'occuper du create mais aussi d'aller chercher un livre via l'API de google books)</t>
   </si>
 </sst>
 </file>
@@ -1225,10 +1237,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>925</c:v>
+                  <c:v>985</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1185</c:v>
+                  <c:v>1530</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2080,16 +2092,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.40217391304347827</c:v>
+                  <c:v>0.36414048059149723</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.51521739130434785</c:v>
+                  <c:v>0.56561922365988915</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9565217391304349E-2</c:v>
+                  <c:v>1.6635859519408502E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4324,7 +4336,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>38 heures 20 minutes</v>
+        <v>45 heures 5 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4339,15 +4351,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>1440</v>
+        <v>1740</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>860</v>
+        <v>965</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>2300</v>
+        <v>2705</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5099,51 +5111,89 @@
       <c r="G37" s="40"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="62" t="str">
+      <c r="A38" s="62">
         <f>IF(ISBLANK(B38),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B38))</f>
-        <v/>
-      </c>
-      <c r="B38" s="30"/>
+        <v>7</v>
+      </c>
+      <c r="B38" s="30">
+        <v>46066</v>
+      </c>
       <c r="C38" s="31"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="22"/>
+      <c r="D38" s="32">
+        <v>45</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>59</v>
+      </c>
       <c r="G38" s="39"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="str">
+      <c r="A39" s="63">
         <f>IF(ISBLANK(B39),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B39))</f>
-        <v/>
-      </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="22"/>
+        <v>7</v>
+      </c>
+      <c r="B39" s="34">
+        <v>46066</v>
+      </c>
+      <c r="C39" s="35">
+        <v>1</v>
+      </c>
+      <c r="D39" s="36">
+        <v>0</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>61</v>
+      </c>
       <c r="G39" s="40"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="62" t="str">
+      <c r="A40" s="62">
         <f>IF(ISBLANK(B40),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B40))</f>
-        <v/>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="22"/>
+        <v>7</v>
+      </c>
+      <c r="B40" s="30">
+        <v>46066</v>
+      </c>
+      <c r="C40" s="31">
+        <v>1</v>
+      </c>
+      <c r="D40" s="32">
+        <v>15</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="G40" s="39"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="63" t="str">
+      <c r="A41" s="63">
         <f>IF(ISBLANK(B41),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B41))</f>
-        <v/>
-      </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="22"/>
+        <v>7</v>
+      </c>
+      <c r="B41" s="34">
+        <v>46066</v>
+      </c>
+      <c r="C41" s="35">
+        <v>3</v>
+      </c>
+      <c r="D41" s="36">
+        <v>45</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>62</v>
+      </c>
       <c r="G41" s="40"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -11172,7 +11222,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
@@ -11180,7 +11230,7 @@
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>925</v>
+        <v>985</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11188,11 +11238,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>15 h 25 min</v>
+        <v>16 h 25 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.40217391304347827</v>
+        <v>0.36414048059149723</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11209,15 +11259,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>900</v>
+        <v>1140</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>285</v>
+        <v>390</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>1185</v>
+        <v>1530</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11225,11 +11275,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>19 h 45 min</v>
+        <v>25 h 30 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.51521739130434785</v>
+        <v>0.56561922365988915</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11303,7 +11353,7 @@
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>1.9565217391304349E-2</v>
+        <v>1.6635859519408502E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11339,7 +11389,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>6.3043478260869562E-2</v>
+        <v>5.3604436229205174E-2</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11355,26 +11405,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>1440</v>
+        <v>1740</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>860</v>
+        <v>965</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>2300</v>
+        <v>2705</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>38 h 20 min</v>
+        <v>45 h 05 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.42592592592592593</v>
+        <v>0.50092592592592589</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>
@@ -11413,15 +11463,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="dfbaf9a740889adeb1cda0be194d08b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f25723b2930dbb90e2332f0c8c46e31" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11622,6 +11663,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11634,14 +11684,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F8341A-4C75-4689-8311-30F611A1EC8F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11660,6 +11702,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA244B3D-6C3D-4F3E-9367-087BFD6AF679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BCB170-39CD-4F0C-9BEB-61E641A4195F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="67">
   <si>
     <t>Auteur:</t>
   </si>
@@ -230,6 +230,18 @@
   </si>
   <si>
     <t>Création des routes simple (get livre) et create livre pas encore fini (il faut s'occuper du create mais aussi d'aller chercher un livre via l'API de google books)</t>
+  </si>
+  <si>
+    <t>Discussion avec Sofiène</t>
+  </si>
+  <si>
+    <t>Route Books et Users de l'API (utilisation de l'API google pour ajouter des livres)</t>
+  </si>
+  <si>
+    <t>J'ai essayé de tester les routes login et register de plusieurs manières mais pour l'instant ce n'est pas vraiment au point</t>
+  </si>
+  <si>
+    <t>Regroupement d'informations dans le rapport (sous forme brutes pour l'instant sans aucune mise en page ou autre)</t>
   </si>
 </sst>
 </file>
@@ -1240,16 +1252,16 @@
                   <c:v>985</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1530</c:v>
+                  <c:v>1860</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>145</c:v>
+                  <c:v>165</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2092,16 +2104,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.36414048059149723</c:v>
+                  <c:v>0.31877022653721682</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.56561922365988915</c:v>
+                  <c:v>0.60194174757281549</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6635859519408502E-2</c:v>
+                  <c:v>2.5889967637540454E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4336,7 +4348,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>45 heures 5 minutes</v>
+        <v>51 heures 30 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4351,15 +4363,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>1740</v>
+        <v>2040</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>965</v>
+        <v>1050</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>2705</v>
+        <v>3090</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5197,51 +5209,87 @@
       <c r="G41" s="40"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="str">
+      <c r="A42" s="62">
         <f>IF(ISBLANK(B42),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B42))</f>
-        <v/>
-      </c>
-      <c r="B42" s="30"/>
+        <v>9</v>
+      </c>
+      <c r="B42" s="30">
+        <v>46076</v>
+      </c>
       <c r="C42" s="31"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="22"/>
+      <c r="D42" s="32">
+        <v>20</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>63</v>
+      </c>
       <c r="G42" s="39"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="63" t="str">
+      <c r="A43" s="63">
         <f>IF(ISBLANK(B43),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B43))</f>
-        <v/>
-      </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B43" s="34">
+        <v>46076</v>
+      </c>
+      <c r="C43" s="35">
+        <v>4</v>
+      </c>
+      <c r="D43" s="36">
+        <v>30</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>64</v>
+      </c>
       <c r="G43" s="40"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="62" t="str">
+      <c r="A44" s="62">
         <f>IF(ISBLANK(B44),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B44))</f>
-        <v/>
-      </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B44" s="30">
+        <v>46076</v>
+      </c>
+      <c r="C44" s="31">
+        <v>1</v>
+      </c>
+      <c r="D44" s="32">
+        <v>0</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>65</v>
+      </c>
       <c r="G44" s="39"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="63" t="str">
+      <c r="A45" s="63">
         <f>IF(ISBLANK(B45),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B45))</f>
-        <v/>
-      </c>
-      <c r="B45" s="34"/>
+        <v>9</v>
+      </c>
+      <c r="B45" s="34">
+        <v>46079</v>
+      </c>
       <c r="C45" s="35"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="22"/>
+      <c r="D45" s="36">
+        <v>35</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>66</v>
+      </c>
       <c r="G45" s="40"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -11242,7 +11290,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.36414048059149723</v>
+        <v>0.31877022653721682</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11259,15 +11307,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>1140</v>
+        <v>1440</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>1530</v>
+        <v>1860</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11275,11 +11323,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>25 h 30 min</v>
+        <v>31 h 00 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.56561922365988915</v>
+        <v>0.60194174757281549</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11337,11 +11385,11 @@
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11349,11 +11397,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>0 h 45 min</v>
+        <v>1 h 20 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>1.6635859519408502E-2</v>
+        <v>2.5889967637540454E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11374,22 +11422,22 @@
       </c>
       <c r="B10">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E10,'Journal de travail'!$D$7:$D$532)</f>
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E10" s="78" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="79" t="str">
         <f t="shared" ref="F10" si="4">QUOTIENT(SUM(A10:B10),60)&amp;" h "&amp;TEXT(MOD(SUM(A10:B10),60), "00")&amp;" min"</f>
-        <v>2 h 25 min</v>
+        <v>2 h 45 min</v>
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>5.3604436229205174E-2</v>
+        <v>5.3398058252427182E-2</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11405,26 +11453,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>1740</v>
+        <v>2040</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>965</v>
+        <v>1050</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>2705</v>
+        <v>3090</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>45 h 05 min</v>
+        <v>51 h 30 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.50092592592592589</v>
+        <v>0.57222222222222219</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>
@@ -11463,6 +11511,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="dfbaf9a740889adeb1cda0be194d08b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f25723b2930dbb90e2332f0c8c46e31" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11663,15 +11720,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11684,6 +11732,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F8341A-4C75-4689-8311-30F611A1EC8F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11702,14 +11758,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BCB170-39CD-4F0C-9BEB-61E641A4195F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BE8DB0-7A16-4855-B3B8-02240D747F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
   <si>
     <t>Auteur:</t>
   </si>
@@ -242,6 +242,24 @@
   </si>
   <si>
     <t>Regroupement d'informations dans le rapport (sous forme brutes pour l'instant sans aucune mise en page ou autre)</t>
+  </si>
+  <si>
+    <t>Page de connexion avec Vue js (se connecter à un user présent dans la db)</t>
+  </si>
+  <si>
+    <t>Discussion avec M. Meylan concernant le projet, il m'a montré comment je pourrais faire pour mieux structurer mon code en découpant et en faisant des "store" le frontend, et aussi en quoi utiliser localstorage peut s'avérer pratique, donc je pense qu'à partir de demain je vais commencer ça</t>
+  </si>
+  <si>
+    <t>Retourner liste de livre (simplement dans la console pour l'instant) mais sachant que la route qui recupere la liste des livres a besoin d'un authentification ce n'est pas si simple, donc actuellement c'est bon j'ai réussis (très très moche et inutilisable mais au moins je sais comment faire)</t>
+  </si>
+  <si>
+    <t>Implémentation store avec pinia + page de connexion fonctionnel, qui redirige vers homepage une fois qu'on est connecté</t>
+  </si>
+  <si>
+    <t>J'ai réfléchi à comment je voudrais que mes pages soient gérer, car je n'ai pas réussi à faire comme je le voulais instinctivement (router.push directement dans un componenent, peut-etre uqe j'ai mal fais mais quand j'essayais ma page web crashait complétement)</t>
+  </si>
+  <si>
+    <t>Mise en place d'un router pour gérer les différentes pages, parcontre pour l'instant j'ai encore qqproblemes de compréhension mais j'ai limpression qu'une fois que j'aurais compris ce qui me manque ca sera un moyen très simple et efficace pour gérer mes pages.</t>
   </si>
 </sst>
 </file>
@@ -1249,10 +1267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>985</c:v>
+                  <c:v>1105</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1860</c:v>
+                  <c:v>2515</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2104,16 +2122,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.31877022653721682</c:v>
+                  <c:v>0.28589909443725742</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60194174757281549</c:v>
+                  <c:v>0.65071151358344115</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5889967637540454E-2</c:v>
+                  <c:v>2.0698576972833119E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4348,7 +4366,7 @@
       <c r="B3" s="86"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>51 heures 30 minutes</v>
+        <v>64 heures 25 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4363,15 +4381,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>2040</v>
+        <v>2760</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1050</v>
+        <v>1105</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>3090</v>
+        <v>3865</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5293,75 +5311,135 @@
       <c r="G45" s="40"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="62" t="str">
+      <c r="A46" s="62">
         <f>IF(ISBLANK(B46),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B46))</f>
-        <v/>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B46" s="30">
+        <v>46079</v>
+      </c>
+      <c r="C46" s="31">
+        <v>4</v>
+      </c>
+      <c r="D46" s="32">
+        <v>10</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>67</v>
+      </c>
       <c r="G46" s="39"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="63" t="str">
+      <c r="A47" s="63">
         <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
-        <v/>
-      </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B47" s="34">
+        <v>46079</v>
+      </c>
+      <c r="C47" s="35">
+        <v>1</v>
+      </c>
+      <c r="D47" s="36">
+        <v>0</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>69</v>
+      </c>
       <c r="G47" s="40"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="62" t="str">
+      <c r="A48" s="62">
         <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
-        <v/>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B48" s="30">
+        <v>46079</v>
+      </c>
+      <c r="C48" s="31">
+        <v>1</v>
+      </c>
+      <c r="D48" s="32">
+        <v>0</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>68</v>
+      </c>
       <c r="G48" s="39"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="63" t="str">
+      <c r="A49" s="63">
         <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
-        <v/>
-      </c>
-      <c r="B49" s="34"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B49" s="34">
+        <v>46080</v>
+      </c>
+      <c r="C49" s="35">
+        <v>3</v>
+      </c>
+      <c r="D49" s="36">
+        <v>45</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>70</v>
+      </c>
       <c r="G49" s="40"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="62" t="str">
+      <c r="A50" s="62">
         <f>IF(ISBLANK(B50),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B50))</f>
-        <v/>
-      </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B50" s="30">
+        <v>46080</v>
+      </c>
+      <c r="C50" s="31">
+        <v>1</v>
+      </c>
+      <c r="D50" s="32">
+        <v>0</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>71</v>
+      </c>
       <c r="G50" s="39"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="63" t="str">
+      <c r="A51" s="63">
         <f>IF(ISBLANK(B51),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B51))</f>
-        <v/>
-      </c>
-      <c r="B51" s="34"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="22"/>
+        <v>9</v>
+      </c>
+      <c r="B51" s="34">
+        <v>46080</v>
+      </c>
+      <c r="C51" s="35">
+        <v>2</v>
+      </c>
+      <c r="D51" s="36">
+        <v>0</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="G51" s="40"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -11270,7 +11348,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>540</v>
+        <v>660</v>
       </c>
       <c r="B6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$D$7:$D$532)</f>
@@ -11278,7 +11356,7 @@
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C10" si="0">SUM(A6:B6)</f>
-        <v>985</v>
+        <v>1105</v>
       </c>
       <c r="E6" s="70" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11286,11 +11364,11 @@
       </c>
       <c r="F6" s="71" t="str">
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
-        <v>16 h 25 min</v>
+        <v>18 h 25 min</v>
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.31877022653721682</v>
+        <v>0.28589909443725742</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11307,15 +11385,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>1440</v>
+        <v>2040</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>1860</v>
+        <v>2515</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11323,11 +11401,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>31 h 00 min</v>
+        <v>41 h 55 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.60194174757281549</v>
+        <v>0.65071151358344115</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11401,7 +11479,7 @@
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>2.5889967637540454E-2</v>
+        <v>2.0698576972833119E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11437,7 +11515,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>5.3398058252427182E-2</v>
+        <v>4.2690815006468305E-2</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11453,26 +11531,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>2040</v>
+        <v>2760</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>1050</v>
+        <v>1105</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>3090</v>
+        <v>3865</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>51 h 30 min</v>
+        <v>64 h 25 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.57222222222222219</v>
+        <v>0.71574074074074079</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>
@@ -11511,15 +11589,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="dfbaf9a740889adeb1cda0be194d08b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f25723b2930dbb90e2332f0c8c46e31" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11720,6 +11789,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11732,14 +11810,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F8341A-4C75-4689-8311-30F611A1EC8F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11758,6 +11828,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BE8DB0-7A16-4855-B3B8-02240D747F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF8AC57-3E16-4AEB-A59E-4115B593A1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
   <si>
     <t>Auteur:</t>
   </si>
@@ -260,6 +260,18 @@
   </si>
   <si>
     <t>Mise en place d'un router pour gérer les différentes pages, parcontre pour l'instant j'ai encore qqproblemes de compréhension mais j'ai limpression qu'une fois que j'aurais compris ce qui me manque ca sera un moyen très simple et efficace pour gérer mes pages.</t>
+  </si>
+  <si>
+    <t>je suis parti 30mn plutôt pour rattraper un test</t>
+  </si>
+  <si>
+    <t>Toujours les routes et début front-end, je suis entrain de faire en sorte que le store recoivent toutes les données dont jai besoin pour le frontend (pour l'instant je prend tout au chargement de la page meme si c'est pas la meilleure idée en prod c'est juste pour avoir une base simple pour l'instant)</t>
+  </si>
+  <si>
+    <t>Page de catalogue en cours, j'affiche tout les livres et demain je ferai les filtres et la page de détails des livres.</t>
+  </si>
+  <si>
+    <t>Début rédaction rapport au propre</t>
   </si>
 </sst>
 </file>
@@ -527,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -715,6 +727,36 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="16" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1270,16 +1312,16 @@
                   <c:v>1105</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2515</c:v>
+                  <c:v>3380</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80</c:v>
+                  <c:v>305</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>165</c:v>
+                  <c:v>910</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2122,16 +2164,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.28589909443725742</c:v>
+                  <c:v>0.19385964912280701</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.65071151358344115</c:v>
+                  <c:v>0.59298245614035083</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0698576972833119E-2</c:v>
+                  <c:v>5.3508771929824561E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4343,15 +4385,15 @@
       <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="84" t="s">
+      <c r="B2" s="95"/>
+      <c r="C2" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
       <c r="F2" s="5" t="s">
         <v>1</v>
       </c>
@@ -4360,13 +4402,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="86"/>
+      <c r="B3" s="95"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>64 heures 25 minutes</v>
+        <v>95 heures 0 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4381,24 +4423,24 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>2760</v>
+        <v>4320</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1105</v>
+        <v>1380</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>3865</v>
+        <v>5700</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="85"/>
+      <c r="D5" s="94"/>
     </row>
     <row r="6" spans="1:15" s="15" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
@@ -5292,226 +5334,280 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="63">
-        <f>IF(ISBLANK(B45),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B45))</f>
+        <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
         <v>9</v>
       </c>
-      <c r="B45" s="34">
-        <v>46079</v>
-      </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="36">
-        <v>35</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>66</v>
-      </c>
+      <c r="B45" s="84">
+        <v>46077</v>
+      </c>
+      <c r="C45" s="85">
+        <v>5</v>
+      </c>
+      <c r="D45" s="86">
+        <v>15</v>
+      </c>
+      <c r="E45" s="87" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="88"/>
       <c r="G45" s="40"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="62">
-        <f>IF(ISBLANK(B46),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B46))</f>
+        <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
         <v>9</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="84">
+        <v>46078</v>
+      </c>
+      <c r="C46" s="85">
+        <v>6</v>
+      </c>
+      <c r="D46" s="86">
+        <v>45</v>
+      </c>
+      <c r="E46" s="87" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="88"/>
+      <c r="G46" s="39"/>
+    </row>
+    <row r="47" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="63">
+        <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
+        <v>9</v>
+      </c>
+      <c r="B47" s="89">
         <v>46079</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C47" s="90"/>
+      <c r="D47" s="91">
+        <v>35</v>
+      </c>
+      <c r="E47" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="32">
-        <v>10</v>
-      </c>
-      <c r="E46" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" s="39"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="63">
-        <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
-        <v>9</v>
-      </c>
-      <c r="B47" s="34">
-        <v>46079</v>
-      </c>
-      <c r="C47" s="35">
-        <v>1</v>
-      </c>
-      <c r="D47" s="36">
-        <v>0</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>69</v>
+      <c r="F47" s="88" t="s">
+        <v>66</v>
       </c>
       <c r="G47" s="40"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="62">
-        <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
-        <v>9</v>
-      </c>
-      <c r="B48" s="30">
-        <v>46079</v>
-      </c>
-      <c r="C48" s="31">
-        <v>1</v>
-      </c>
-      <c r="D48" s="32">
-        <v>0</v>
-      </c>
-      <c r="E48" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G48" s="39"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="63">
-        <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
-        <v>9</v>
-      </c>
-      <c r="B49" s="34">
-        <v>46080</v>
-      </c>
-      <c r="C49" s="35">
-        <v>3</v>
-      </c>
-      <c r="D49" s="36">
-        <v>45</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G49" s="40"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="62">
         <f>IF(ISBLANK(B50),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B50))</f>
         <v>9</v>
       </c>
-      <c r="B50" s="30">
-        <v>46080</v>
-      </c>
-      <c r="C50" s="31">
-        <v>1</v>
-      </c>
-      <c r="D50" s="32">
-        <v>0</v>
-      </c>
-      <c r="E50" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G50" s="39"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="63">
+      <c r="B48" s="84">
+        <v>46079</v>
+      </c>
+      <c r="C48" s="85">
+        <v>4</v>
+      </c>
+      <c r="D48" s="86">
+        <v>10</v>
+      </c>
+      <c r="E48" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="88" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="39"/>
+    </row>
+    <row r="49" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="63">
         <f>IF(ISBLANK(B51),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B51))</f>
         <v>9</v>
       </c>
-      <c r="B51" s="34">
+      <c r="B49" s="89">
+        <v>46079</v>
+      </c>
+      <c r="C49" s="90">
+        <v>1</v>
+      </c>
+      <c r="D49" s="91">
+        <v>0</v>
+      </c>
+      <c r="E49" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="88" t="s">
+        <v>69</v>
+      </c>
+      <c r="G49" s="40"/>
+    </row>
+    <row r="50" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A50" s="62">
+        <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
+        <v>9</v>
+      </c>
+      <c r="B50" s="84">
+        <v>46079</v>
+      </c>
+      <c r="C50" s="85">
+        <v>1</v>
+      </c>
+      <c r="D50" s="86">
+        <v>0</v>
+      </c>
+      <c r="E50" s="87" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="G50" s="39"/>
+    </row>
+    <row r="51" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="63">
+        <f>IF(ISBLANK(B53),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B53))</f>
+        <v>9</v>
+      </c>
+      <c r="B51" s="89">
         <v>46080</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="90">
+        <v>3</v>
+      </c>
+      <c r="D51" s="91">
+        <v>45</v>
+      </c>
+      <c r="E51" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="40"/>
+    </row>
+    <row r="52" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="62">
+        <f>IF(ISBLANK(B54),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B54))</f>
+        <v>9</v>
+      </c>
+      <c r="B52" s="84">
+        <v>46080</v>
+      </c>
+      <c r="C52" s="85">
+        <v>1</v>
+      </c>
+      <c r="D52" s="86">
+        <v>0</v>
+      </c>
+      <c r="E52" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="D51" s="36">
-        <v>0</v>
-      </c>
-      <c r="E51" s="37" t="s">
+      <c r="F52" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" s="39"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="63" t="e">
+        <f>IF(ISBLANK(#REF!),"",_xlfn.ISOWEEKNUM('Journal de travail'!#REF!))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B53" s="34">
+        <v>46080</v>
+      </c>
+      <c r="C53" s="35">
+        <v>1</v>
+      </c>
+      <c r="D53" s="36">
+        <v>40</v>
+      </c>
+      <c r="E53" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="F53" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="G51" s="40"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="62" t="str">
-        <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
-        <v/>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="39"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="63" t="str">
-        <f>IF(ISBLANK(B53),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B53))</f>
-        <v/>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="22"/>
       <c r="G53" s="40"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="62" t="str">
-        <f>IF(ISBLANK(B54),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B54))</f>
-        <v/>
-      </c>
-      <c r="B54" s="30"/>
+      <c r="A54" s="62" t="e">
+        <f>IF(ISBLANK(#REF!),"",_xlfn.ISOWEEKNUM('Journal de travail'!#REF!))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B54" s="30">
+        <v>46080</v>
+      </c>
       <c r="C54" s="31"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="22"/>
+      <c r="D54" s="32">
+        <v>25</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>73</v>
+      </c>
       <c r="G54" s="39"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="63" t="str">
+      <c r="A55" s="63">
         <f>IF(ISBLANK(B55),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B55))</f>
-        <v/>
-      </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="22"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="34">
+        <v>46083</v>
+      </c>
+      <c r="C55" s="35">
+        <v>5</v>
+      </c>
+      <c r="D55" s="36">
+        <v>15</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>74</v>
+      </c>
       <c r="G55" s="40"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="62" t="str">
+    <row r="56" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="62">
         <f>IF(ISBLANK(B56),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B56))</f>
-        <v/>
-      </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="39"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="30">
+        <v>46084</v>
+      </c>
+      <c r="C56" s="31">
+        <v>6</v>
+      </c>
+      <c r="D56" s="32">
+        <v>45</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="G56" s="39"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="63" t="str">
+      <c r="A57" s="63">
         <f>IF(ISBLANK(B57),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B57))</f>
-        <v/>
-      </c>
-      <c r="B57" s="34"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="34">
+        <v>46086</v>
+      </c>
+      <c r="C57" s="35">
+        <v>3</v>
+      </c>
+      <c r="D57" s="36">
+        <v>45</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="40" t="s">
+        <v>76</v>
+      </c>
       <c r="G57" s="40"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -5520,9 +5616,15 @@
         <v/>
       </c>
       <c r="B58" s="30"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="33"/>
+      <c r="C58" s="31">
+        <v>2</v>
+      </c>
+      <c r="D58" s="32">
+        <v>45</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>19</v>
+      </c>
       <c r="F58" s="39"/>
       <c r="G58" s="39"/>
     </row>
@@ -11222,7 +11324,7 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7:E532">
+  <conditionalFormatting sqref="E7:E44 E47:E532">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>$E7="Absent"</formula>
     </cfRule>
@@ -11252,13 +11354,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C532" xr:uid="{9D52E29F-610D-40B2-B3CC-F94A741DD978}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C44 C47:C532" xr:uid="{9D52E29F-610D-40B2-B3CC-F94A741DD978}">
       <formula1>$N$7:$N$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D532" xr:uid="{46510F84-8BCC-4BD6-9A19-9F03ACD74D05}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D44 D47:D532" xr:uid="{46510F84-8BCC-4BD6-9A19-9F03ACD74D05}">
       <formula1>$O$7:$O$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E532" xr:uid="{EBCA439E-C5F1-BC4C-88EE-2BB045537E3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E44 E47:E532" xr:uid="{EBCA439E-C5F1-BC4C-88EE-2BB045537E3E}">
       <formula1>$M$7:$M$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -11368,7 +11470,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.28589909443725742</v>
+        <v>0.19385964912280701</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11385,15 +11487,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>2040</v>
+        <v>2760</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>475</v>
+        <v>620</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>2515</v>
+        <v>3380</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11401,11 +11503,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>41 h 55 min</v>
+        <v>56 h 20 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.65071151358344115</v>
+        <v>0.59298245614035083</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11459,15 +11561,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11475,11 +11577,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>1 h 20 min</v>
+        <v>5 h 05 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>2.0698576972833119E-2</v>
+        <v>5.3508771929824561E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11496,26 +11598,26 @@
     <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E10,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="B10">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E10,'Journal de travail'!$D$7:$D$532)</f>
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>910</v>
       </c>
       <c r="E10" s="78" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="79" t="str">
         <f t="shared" ref="F10" si="4">QUOTIENT(SUM(A10:B10),60)&amp;" h "&amp;TEXT(MOD(SUM(A10:B10),60), "00")&amp;" min"</f>
-        <v>2 h 45 min</v>
+        <v>15 h 10 min</v>
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>4.2690815006468305E-2</v>
+        <v>0.15964912280701754</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11531,26 +11633,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>2760</v>
+        <v>4320</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>1105</v>
+        <v>1380</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>3865</v>
+        <v>5700</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>64 h 25 min</v>
+        <v>95 h 00 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>0.71574074074074079</v>
+        <v>1.0555555555555556</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF8AC57-3E16-4AEB-A59E-4115B593A1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE859C-77AE-41C4-8378-6EB1C237D457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>Auteur:</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>Début rédaction rapport au propre</t>
+  </si>
+  <si>
+    <t>Rédiger texte fonctionnelles</t>
+  </si>
+  <si>
+    <t>Les filtres sont fais + page détails + page de profile</t>
+  </si>
+  <si>
+    <t>Système de pagination + afficher emprunts livre dans page profile  + register + séparation page catalogue en component partial (Je l'avais fais mais pas assez donc il faut que je découpe encore, pour pouvoir réutilisr ces composant dans l'interface admin par exemple) + demain ducoup continuer découpage en component + petit + interface admin + rapport de projet + doc mise en place</t>
   </si>
 </sst>
 </file>
@@ -1312,13 +1321,13 @@
                   <c:v>1105</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3380</c:v>
+                  <c:v>4085</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>305</c:v>
+                  <c:v>410</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>910</c:v>
@@ -2164,16 +2173,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.19385964912280701</c:v>
+                  <c:v>0.16973886328725038</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.59298245614035083</c:v>
+                  <c:v>0.62749615975422424</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.3508771929824561E-2</c:v>
+                  <c:v>6.2980030721966201E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4408,7 +4417,7 @@
       <c r="B3" s="95"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>95 heures 0 minutes</v>
+        <v>108 heures 30 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4423,15 +4432,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>4320</v>
+        <v>5040</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1380</v>
+        <v>1470</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>5700</v>
+        <v>6510</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5611,11 +5620,13 @@
       <c r="G57" s="40"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="62" t="str">
+      <c r="A58" s="62">
         <f>IF(ISBLANK(B58),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B58))</f>
-        <v/>
-      </c>
-      <c r="B58" s="30"/>
+        <v>10</v>
+      </c>
+      <c r="B58" s="30">
+        <v>46086</v>
+      </c>
       <c r="C58" s="31">
         <v>2</v>
       </c>
@@ -5665,23 +5676,35 @@
       <c r="G61" s="40"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="62" t="str">
+      <c r="A62" s="62">
         <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
-        <v/>
-      </c>
-      <c r="B62" s="30"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="B62" s="30">
+        <v>46090</v>
+      </c>
+      <c r="C62" s="31">
+        <v>6</v>
+      </c>
+      <c r="D62" s="32">
+        <v>45</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="39" t="s">
+        <v>78</v>
+      </c>
       <c r="G62" s="39"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="63" t="str">
+      <c r="A63" s="63">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
-        <v/>
-      </c>
-      <c r="B63" s="34"/>
+        <v>11</v>
+      </c>
+      <c r="B63" s="34">
+        <v>46090</v>
+      </c>
       <c r="C63" s="35"/>
       <c r="D63" s="36"/>
       <c r="E63" s="37"/>
@@ -5689,11 +5712,13 @@
       <c r="G63" s="40"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="62" t="str">
+      <c r="A64" s="62">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
-        <v/>
-      </c>
-      <c r="B64" s="30"/>
+        <v>11</v>
+      </c>
+      <c r="B64" s="30">
+        <v>46090</v>
+      </c>
       <c r="C64" s="31"/>
       <c r="D64" s="32"/>
       <c r="E64" s="33"/>
@@ -5701,35 +5726,57 @@
       <c r="G64" s="39"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="63" t="str">
+      <c r="A65" s="63">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
-        <v/>
-      </c>
-      <c r="B65" s="34"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="40"/>
+        <v>11</v>
+      </c>
+      <c r="B65" s="34">
+        <v>46091</v>
+      </c>
+      <c r="C65" s="35">
+        <v>1</v>
+      </c>
+      <c r="D65" s="36">
+        <v>45</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="40" t="s">
+        <v>77</v>
+      </c>
       <c r="G65" s="40"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="62" t="str">
+    <row r="66" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="62">
         <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
-        <v/>
-      </c>
-      <c r="B66" s="30"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="B66" s="30">
+        <v>46091</v>
+      </c>
+      <c r="C66" s="31">
+        <v>5</v>
+      </c>
+      <c r="D66" s="32">
+        <v>0</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="G66" s="39"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="63" t="str">
+      <c r="A67" s="63">
         <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
-        <v/>
-      </c>
-      <c r="B67" s="34"/>
+        <v>11</v>
+      </c>
+      <c r="B67" s="34">
+        <v>46091</v>
+      </c>
       <c r="C67" s="35"/>
       <c r="D67" s="36"/>
       <c r="E67" s="37"/>
@@ -11470,7 +11517,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.19385964912280701</v>
+        <v>0.16973886328725038</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11487,15 +11534,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>2760</v>
+        <v>3420</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>620</v>
+        <v>665</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>3380</v>
+        <v>4085</v>
       </c>
       <c r="E7" s="73" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11503,11 +11550,11 @@
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" ref="F7:F11" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>56 h 20 min</v>
+        <v>68 h 05 min</v>
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.59298245614035083</v>
+        <v>0.62749615975422424</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11561,15 +11608,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>305</v>
+        <v>410</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11577,11 +11624,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>5 h 05 min</v>
+        <v>6 h 50 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>5.3508771929824561E-2</v>
+        <v>6.2980030721966201E-2</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11617,7 +11664,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.15964912280701754</v>
+        <v>0.13978494623655913</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11633,26 +11680,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>4320</v>
+        <v>5040</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>1380</v>
+        <v>1470</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>5700</v>
+        <v>6510</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>95 h 00 min</v>
+        <v>108 h 30 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>1.0555555555555556</v>
+        <v>1.2055555555555555</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE859C-77AE-41C4-8378-6EB1C237D457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1EB07C-943C-45CE-B1F8-D5D4FF1F8D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
   <si>
     <t>Auteur:</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Système de pagination + afficher emprunts livre dans page profile  + register + séparation page catalogue en component partial (Je l'avais fais mais pas assez donc il faut que je découpe encore, pour pouvoir réutilisr ces composant dans l'interface admin par exemple) + demain ducoup continuer découpage en component + petit + interface admin + rapport de projet + doc mise en place</t>
+  </si>
+  <si>
+    <t>Rédaction Rapport (Création schéma technique etc), demain finir rapport, faire release TOUT CLEAN + pas oublier tester les test et commenter selon résultat, pq ca marche pas etcetc</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1330,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>410</c:v>
+                  <c:v>815</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>910</c:v>
@@ -2173,16 +2176,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.16973886328725038</c:v>
+                  <c:v>0.15979754157628345</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.62749615975422424</c:v>
+                  <c:v>0.59074475777295732</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.2980030721966201E-2</c:v>
+                  <c:v>0.11785972523499638</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4417,7 +4420,7 @@
       <c r="B3" s="95"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>108 heures 30 minutes</v>
+        <v>115 heures 15 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4432,15 +4435,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>5040</v>
+        <v>5400</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1470</v>
+        <v>1515</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>6510</v>
+        <v>6915</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5640,71 +5643,99 @@
       <c r="G58" s="39"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="63" t="str">
+      <c r="A59" s="63" t="e">
+        <f>IF(ISBLANK(#REF!),"",_xlfn.ISOWEEKNUM('Journal de travail'!#REF!))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B59" s="30">
+        <v>46090</v>
+      </c>
+      <c r="C59" s="31">
+        <v>6</v>
+      </c>
+      <c r="D59" s="32">
+        <v>45</v>
+      </c>
+      <c r="E59" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="G59" s="40"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="62" t="e">
+        <f>IF(ISBLANK(#REF!),"",_xlfn.ISOWEEKNUM('Journal de travail'!#REF!))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B60" s="34">
+        <v>46092</v>
+      </c>
+      <c r="C60" s="35">
+        <v>1</v>
+      </c>
+      <c r="D60" s="36">
+        <v>45</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" s="39"/>
+    </row>
+    <row r="61" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="63" t="e">
+        <f>IF(ISBLANK(#REF!),"",_xlfn.ISOWEEKNUM('Journal de travail'!#REF!))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B61" s="30">
+        <v>46092</v>
+      </c>
+      <c r="C61" s="31">
+        <v>5</v>
+      </c>
+      <c r="D61" s="32">
+        <v>0</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="G61" s="40"/>
+    </row>
+    <row r="62" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="62">
         <f>IF(ISBLANK(B59),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B59))</f>
-        <v/>
-      </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="62" t="str">
-        <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
-        <v/>
-      </c>
-      <c r="B60" s="30"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="63" t="str">
-        <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
-        <v/>
-      </c>
-      <c r="B61" s="34"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="40"/>
-      <c r="G61" s="40"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="62">
-        <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
         <v>11</v>
       </c>
-      <c r="B62" s="30">
-        <v>46090</v>
-      </c>
-      <c r="C62" s="31">
+      <c r="B62" s="34">
+        <v>46093</v>
+      </c>
+      <c r="C62" s="35">
         <v>6</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="36">
         <v>45</v>
       </c>
-      <c r="E62" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>78</v>
+      <c r="E62" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>80</v>
       </c>
       <c r="G62" s="39"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="63">
+      <c r="A63" s="63" t="str">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
-        <v>11</v>
-      </c>
-      <c r="B63" s="34">
-        <v>46090</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B63" s="34"/>
       <c r="C63" s="35"/>
       <c r="D63" s="36"/>
       <c r="E63" s="37"/>
@@ -5712,13 +5743,11 @@
       <c r="G63" s="40"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="62">
+      <c r="A64" s="62" t="str">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
-        <v>11</v>
-      </c>
-      <c r="B64" s="30">
-        <v>46090</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B64" s="30"/>
       <c r="C64" s="31"/>
       <c r="D64" s="32"/>
       <c r="E64" s="33"/>
@@ -5727,60 +5756,38 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="63">
-        <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
+        <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v>11</v>
       </c>
-      <c r="B65" s="34">
-        <v>46091</v>
-      </c>
-      <c r="C65" s="35">
-        <v>1</v>
-      </c>
-      <c r="D65" s="36">
-        <v>45</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" s="40" t="s">
-        <v>77</v>
-      </c>
+      <c r="B65" s="84"/>
+      <c r="C65" s="85"/>
+      <c r="D65" s="86"/>
+      <c r="E65" s="87"/>
+      <c r="F65" s="88"/>
       <c r="G65" s="40"/>
     </row>
-    <row r="66" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="62">
-        <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
+        <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
         <v>11</v>
       </c>
-      <c r="B66" s="30">
-        <v>46091</v>
-      </c>
-      <c r="C66" s="31">
-        <v>5</v>
-      </c>
-      <c r="D66" s="32">
-        <v>0</v>
-      </c>
-      <c r="E66" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" s="39" t="s">
-        <v>79</v>
-      </c>
+      <c r="B66" s="84"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="86"/>
+      <c r="E66" s="87"/>
+      <c r="F66" s="88"/>
       <c r="G66" s="39"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="63">
-        <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
+        <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
         <v>11</v>
       </c>
-      <c r="B67" s="34">
-        <v>46091</v>
-      </c>
-      <c r="C67" s="35"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="40"/>
+      <c r="B67" s="84"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="86"/>
+      <c r="E67" s="87"/>
+      <c r="F67" s="88"/>
       <c r="G67" s="40"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -11371,7 +11378,7 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7:E44 E47:E532">
+  <conditionalFormatting sqref="E7:E44 E68:E532 E47:E64">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>$E7="Absent"</formula>
     </cfRule>
@@ -11401,13 +11408,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C44 C47:C532" xr:uid="{9D52E29F-610D-40B2-B3CC-F94A741DD978}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C44 C47:C64 C68:C532" xr:uid="{9D52E29F-610D-40B2-B3CC-F94A741DD978}">
       <formula1>$N$7:$N$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D44 D47:D532" xr:uid="{46510F84-8BCC-4BD6-9A19-9F03ACD74D05}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D44 D47:D64 D68:D532" xr:uid="{46510F84-8BCC-4BD6-9A19-9F03ACD74D05}">
       <formula1>$O$7:$O$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E44 E47:E532" xr:uid="{EBCA439E-C5F1-BC4C-88EE-2BB045537E3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E44 E47:E64 E68:E532" xr:uid="{EBCA439E-C5F1-BC4C-88EE-2BB045537E3E}">
       <formula1>$M$7:$M$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -11517,7 +11524,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.16973886328725038</v>
+        <v>0.15979754157628345</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11554,7 +11561,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.62749615975422424</v>
+        <v>0.59074475777295732</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11608,15 +11615,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>410</v>
+        <v>815</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11624,11 +11631,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>6 h 50 min</v>
+        <v>13 h 35 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>6.2980030721966201E-2</v>
+        <v>0.11785972523499638</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11664,7 +11671,7 @@
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.13978494623655913</v>
+        <v>0.13159797541576285</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11680,26 +11687,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>5040</v>
+        <v>5400</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>1470</v>
+        <v>1515</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>6510</v>
+        <v>6915</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>108 h 30 min</v>
+        <v>115 h 15 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>1.2055555555555555</v>
+        <v>1.2805555555555554</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1EB07C-943C-45CE-B1F8-D5D4FF1F8D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F714C7C-BE3B-4EE2-B625-C4FDC62C8AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <si>
     <t>Auteur:</t>
   </si>
@@ -284,6 +284,21 @@
   </si>
   <si>
     <t>Rédaction Rapport (Création schéma technique etc), demain finir rapport, faire release TOUT CLEAN + pas oublier tester les test et commenter selon résultat, pq ca marche pas etcetc</t>
+  </si>
+  <si>
+    <t>Tester les divers tests fonctionnels, documenter les résultats dans le rapport et expliquer les résultats</t>
+  </si>
+  <si>
+    <t>Description implémentation</t>
+  </si>
+  <si>
+    <t>Rédaction rapport (conclusion, comparaison planif + travail effectué + faire livrable + glossaire + résumé)</t>
+  </si>
+  <si>
+    <t>Démonstration site M. Meylan</t>
+  </si>
+  <si>
+    <t>Malade</t>
   </si>
 </sst>
 </file>
@@ -1327,13 +1342,13 @@
                   <c:v>4085</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>815</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>910</c:v>
+                  <c:v>920</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2176,16 +2191,16 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.15979754157628345</c:v>
+                  <c:v>0.15136986301369862</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.59074475777295732</c:v>
+                  <c:v>0.55958904109589036</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.2328767123287671E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11785972523499638</c:v>
+                  <c:v>0.15068493150684931</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4420,7 +4435,7 @@
       <c r="B3" s="95"/>
       <c r="C3" s="67" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>115 heures 15 minutes</v>
+        <v>121 heures 40 minutes</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="3"/>
@@ -4435,15 +4450,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="17">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>5400</v>
+        <v>5700</v>
       </c>
       <c r="D4" s="17">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>1515</v>
+        <v>1600</v>
       </c>
       <c r="E4" s="24">
         <f>SUM(C4:D4)</f>
-        <v>6915</v>
+        <v>7300</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -5358,10 +5373,12 @@
       <c r="D45" s="86">
         <v>15</v>
       </c>
-      <c r="E45" s="87" t="s">
+      <c r="E45" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="88"/>
+      <c r="F45" s="88" t="s">
+        <v>85</v>
+      </c>
       <c r="G45" s="40"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,10 +5395,12 @@
       <c r="D46" s="86">
         <v>45</v>
       </c>
-      <c r="E46" s="87" t="s">
+      <c r="E46" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="88"/>
+      <c r="F46" s="88" t="s">
+        <v>85</v>
+      </c>
       <c r="G46" s="39"/>
     </row>
     <row r="47" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -5731,39 +5750,67 @@
       <c r="G62" s="39"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="63" t="str">
+      <c r="A63" s="63">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
-        <v/>
-      </c>
-      <c r="B63" s="34"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="40"/>
+        <v>11</v>
+      </c>
+      <c r="B63" s="34">
+        <v>46094</v>
+      </c>
+      <c r="C63" s="35">
+        <v>2</v>
+      </c>
+      <c r="D63" s="36">
+        <v>30</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>82</v>
+      </c>
       <c r="G63" s="40"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="62" t="str">
+    <row r="64" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="62">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
-        <v/>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="B64" s="30">
+        <v>46094</v>
+      </c>
+      <c r="C64" s="31">
+        <v>1</v>
+      </c>
+      <c r="D64" s="32">
+        <v>30</v>
+      </c>
+      <c r="E64" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="39" t="s">
+        <v>81</v>
+      </c>
       <c r="G64" s="39"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" s="63">
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v>11</v>
       </c>
       <c r="B65" s="84"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="86"/>
-      <c r="E65" s="87"/>
-      <c r="F65" s="88"/>
+      <c r="C65" s="85">
+        <v>2</v>
+      </c>
+      <c r="D65" s="86">
+        <v>15</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="88" t="s">
+        <v>83</v>
+      </c>
       <c r="G65" s="40"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -5773,9 +5820,15 @@
       </c>
       <c r="B66" s="84"/>
       <c r="C66" s="85"/>
-      <c r="D66" s="86"/>
-      <c r="E66" s="87"/>
-      <c r="F66" s="88"/>
+      <c r="D66" s="86">
+        <v>10</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66" s="88" t="s">
+        <v>84</v>
+      </c>
       <c r="G66" s="39"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -5786,7 +5839,7 @@
       <c r="B67" s="84"/>
       <c r="C67" s="85"/>
       <c r="D67" s="86"/>
-      <c r="E67" s="87"/>
+      <c r="E67" s="33"/>
       <c r="F67" s="88"/>
       <c r="G67" s="40"/>
     </row>
@@ -5798,7 +5851,7 @@
       <c r="B68" s="30"/>
       <c r="C68" s="31"/>
       <c r="D68" s="32"/>
-      <c r="E68" s="33"/>
+      <c r="E68" s="87"/>
       <c r="F68" s="39"/>
       <c r="G68" s="39"/>
     </row>
@@ -5810,7 +5863,7 @@
       <c r="B69" s="34"/>
       <c r="C69" s="35"/>
       <c r="D69" s="36"/>
-      <c r="E69" s="37"/>
+      <c r="E69" s="87"/>
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
     </row>
@@ -5822,7 +5875,7 @@
       <c r="B70" s="30"/>
       <c r="C70" s="31"/>
       <c r="D70" s="32"/>
-      <c r="E70" s="33"/>
+      <c r="E70" s="87"/>
       <c r="F70" s="39"/>
       <c r="G70" s="39"/>
     </row>
@@ -5834,7 +5887,7 @@
       <c r="B71" s="34"/>
       <c r="C71" s="35"/>
       <c r="D71" s="36"/>
-      <c r="E71" s="37"/>
+      <c r="E71" s="87"/>
       <c r="F71" s="40"/>
       <c r="G71" s="40"/>
     </row>
@@ -5846,7 +5899,7 @@
       <c r="B72" s="30"/>
       <c r="C72" s="31"/>
       <c r="D72" s="32"/>
-      <c r="E72" s="33"/>
+      <c r="E72" s="87"/>
       <c r="F72" s="39"/>
       <c r="G72" s="39"/>
     </row>
@@ -11378,7 +11431,7 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7:E44 E68:E532 E47:E64">
+  <conditionalFormatting sqref="E73:E532 E7:E67">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>$E7="Absent"</formula>
     </cfRule>
@@ -11414,7 +11467,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D44 D47:D64 D68:D532" xr:uid="{46510F84-8BCC-4BD6-9A19-9F03ACD74D05}">
       <formula1>$O$7:$O$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E44 E47:E64 E68:E532" xr:uid="{EBCA439E-C5F1-BC4C-88EE-2BB045537E3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E47:E67 E46 E7:E45 E73:E532" xr:uid="{EBCA439E-C5F1-BC4C-88EE-2BB045537E3E}">
       <formula1>$M$7:$M$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -11524,7 +11577,7 @@
       </c>
       <c r="G6" s="72">
         <f>SUM(A6:B6)/$C$11</f>
-        <v>0.15979754157628345</v>
+        <v>0.15136986301369862</v>
       </c>
       <c r="L6" s="51" t="str">
         <f>'Journal de travail'!M8</f>
@@ -11561,7 +11614,7 @@
       </c>
       <c r="G7" s="75">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$11</f>
-        <v>0.59074475777295732</v>
+        <v>0.55958904109589036</v>
       </c>
       <c r="L7" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -11578,15 +11631,15 @@
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E8,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E8,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E8" s="76" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11594,11 +11647,11 @@
       </c>
       <c r="F8" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>0 h 00 min</v>
+        <v>1 h 30 min</v>
       </c>
       <c r="G8" s="72">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.2328767123287671E-2</v>
       </c>
       <c r="L8" s="54" t="str">
         <f>'Journal de travail'!M10</f>
@@ -11615,15 +11668,15 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="B9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$D$7:$D$532)</f>
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>815</v>
+        <v>1100</v>
       </c>
       <c r="E9" s="77" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11631,11 +11684,11 @@
       </c>
       <c r="F9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>13 h 35 min</v>
+        <v>18 h 20 min</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="2"/>
-        <v>0.11785972523499638</v>
+        <v>0.15068493150684931</v>
       </c>
       <c r="L9" s="55" t="str">
         <f>'Journal de travail'!M11</f>
@@ -11656,22 +11709,22 @@
       </c>
       <c r="B10">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E10,'Journal de travail'!$D$7:$D$532)</f>
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="E10" s="78" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="79" t="str">
         <f t="shared" ref="F10" si="4">QUOTIENT(SUM(A10:B10),60)&amp;" h "&amp;TEXT(MOD(SUM(A10:B10),60), "00")&amp;" min"</f>
-        <v>15 h 10 min</v>
+        <v>15 h 20 min</v>
       </c>
       <c r="G10" s="80">
         <f>SUM(A10:B10)/$C$11</f>
-        <v>0.13159797541576285</v>
+        <v>0.12602739726027398</v>
       </c>
       <c r="L10" s="69" t="s">
         <v>28</v>
@@ -11687,26 +11740,26 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>SUM(A6:A10)</f>
-        <v>5400</v>
+        <v>5700</v>
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>1515</v>
+        <v>1600</v>
       </c>
       <c r="C11">
         <f>SUM(A11:B11)</f>
-        <v>6915</v>
+        <v>7300</v>
       </c>
       <c r="E11" s="81" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="1"/>
-        <v>115 h 15 min</v>
+        <v>121 h 40 min</v>
       </c>
       <c r="G11" s="82">
         <f>C11/C12</f>
-        <v>1.2805555555555554</v>
+        <v>1.3518518518518519</v>
       </c>
       <c r="L11" s="56" t="s">
         <v>18</v>
@@ -11745,6 +11798,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="dfbaf9a740889adeb1cda0be194d08b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f25723b2930dbb90e2332f0c8c46e31" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11945,15 +12007,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11966,6 +12019,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7F8341A-4C75-4689-8311-30F611A1EC8F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11984,14 +12045,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
+++ b/Journal-de-Travail_MaresJulien_P_Appro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px50vpm\Documents\GitHub\P_Bibliothèque\P_Appro1_Bibliotheque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F714C7C-BE3B-4EE2-B625-C4FDC62C8AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06221EDA-74CD-412D-8198-5F7AB2EED94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -5798,7 +5798,9 @@
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v>11</v>
       </c>
-      <c r="B65" s="84"/>
+      <c r="B65" s="84">
+        <v>46094</v>
+      </c>
       <c r="C65" s="85">
         <v>2</v>
       </c>
@@ -5818,7 +5820,9 @@
         <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
         <v>11</v>
       </c>
-      <c r="B66" s="84"/>
+      <c r="B66" s="84">
+        <v>46094</v>
+      </c>
       <c r="C66" s="85"/>
       <c r="D66" s="86">
         <v>10</v>
